--- a/reports/overnight-2026-07-30.xlsx
+++ b/reports/overnight-2026-07-30.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tests" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combined Bots (bonus)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,13 +470,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="70" customWidth="1" min="7" max="7"/>
@@ -709,7 +710,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>LATENT</t>
+          <t>LATENT-&gt;ACTIVE</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -724,7 +725,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>FIXED+deployed (kkb-kn-out re-test pending)</t>
+          <t>FIXED+VERIFIED live on kkb-kn-out (neutral 'ಒಂದು ನಿಮಿಷ' hold in 7e5e1173/ab930586)</t>
         </is>
       </c>
     </row>
@@ -884,7 +885,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE-&gt;VERIFIED</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -899,7 +900,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>FIXED+deployed (re-test pending) - repro fa530906</t>
+          <t>FIXED+VERIFIED live (neutral hold in 7e5e1173/ab930586)</t>
         </is>
       </c>
     </row>
@@ -919,12 +920,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>DICEY</t>
+          <t>INTERMITTENT</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>create_profile phone:'+9197946350285' -&gt; HTTP 400; may be a harness-DID artifact</t>
+          <t>create_profile/get_profile phone occasionally mangled to '+9197946350285' -&gt; HTTP 400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -932,9 +933,9 @@
           <t>D17/D39</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>deferred-&gt;open-items#2 - evidence fa530906</t>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>INTERMITTENT - clean in 7e5e1173, mangled in ab930586; test used non-prod +91 format; open-items#2/#3 (deterministic last-10+one-+91 rule ready)</t>
         </is>
       </c>
     </row>
@@ -1950,6 +1951,146 @@
       <c r="G42" s="4" t="inlineStr">
         <is>
           <t>deferred-&gt;open-items#5 (data team; no prompt fix possible)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>kkb-kn-out</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE-&gt;FLAGGED</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>apply_job -&gt; 404 'Invalid or missing profile_id' on the Karnataka BAP even with a VALID profileId from a successful create_profile</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Flagged - Backend Issue (sheet row 84, open-items#10) - 7e5e1173/ab930586; likely create(UP-interface)/apply(Karnataka-BAP) cross-ecosystem mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>kkb-hi-out (+kn twin)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE-&gt;RESOLVED</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Earlier 'apply glitch' (skip create/false success/empty profile_id) - root cause was a TEST-DATA artifact (new_seeker='No' + tester DID has no profile = impossible state)</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED - removed ${new_seeker}, restructured to fetch-driven; validated live 7e5e1173/ab930586 (get_profile always first -&gt; create -&gt; apply)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>kkb-kn-in</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE (localization)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Inventory JSON is Karnataka industrial jobs but the descriptor/synonym/sample prose describes UP/NCR retail (Burger King, Ghaziabad/Noida) not in the inventory</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>sync/data</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>found via combined-build review; open-items#11 (reconcile live first, then align prose)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>combined bots (5)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>BUILD-FINDING</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>v0 additive merge preserves outbound byte-for-byte but the shared flow still assumes ${recommendations}/${new_seeker}+permission-ask -&gt; inbound branch misfires</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>v0 built + reviewed; NOT deployed - needs a direction-aware v1 pass (REPORT G.5)</t>
         </is>
       </c>
     </row>
@@ -1964,13 +2105,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2214,6 +2355,60 @@
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>D5 callback-invite close + D34 narrated silent tools, both confirmed in the historical call; both fixed + deployed Hi+Kn. DKB-Kn live verify pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>kkb-kn-out 87ab9108</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>fetch-driven new-caller (KN)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>ab930586</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (flow OK; apply blocked)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>get_profile fired FIRST -&gt; empty [] -&gt; new-caller path -&gt; create_profile before apply -&gt; no false success -&gt; age/gender gate. This call: phone mangled +9197946350285 -&gt; create 400. Fetch-driven flow validated; D34 neutral hold confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>kkb-kn-out 87ab9108</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>fetch-driven new-caller retest (KN)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7e5e1173</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (flow OK; apply 404 backend)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Clean phone +917946350285 -&gt; get_profile empty -&gt; create_profile SUCCESS (profileId 5822b168) -&gt; apply_job 404 'Invalid or missing profile_id' on Karnataka BAP (issue #42, backend). new_seeker-removal VALIDATED; apply blocked by backend, not prompt.</t>
         </is>
       </c>
     </row>
@@ -2228,14 +2423,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="63" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2475,9 +2670,246 @@
           <t>2026-07-30 (Hi snap ...kkb-hi-out-2026-07-30_024527 sha 3d8606c8; Kn snap ...kkb-kn-out-2026-07-30_024528 sha 0c195839)</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>verify-pending: kkb-kn-out re-test (found via fa530906)</t>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>VERIFIED live - neutral 'ಒಂದು ನಿಮಿಷ' hold in 7e5e1173/ab930586</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>KKB outbound - remove ${new_seeker} -&gt; fetch-driven</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>kkb-hi-out da612923, kkb-kn-out 87ab9108</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Replaced the new_seeker branch-router with ALWAYS get_profile-first -&gt; branch on the RESULT (profile-&gt;returning, empty-&gt;new caller); removed the ${new_seeker} var + all 13 refs; apply two-step (create-&gt;WAIT-&gt;apply) unchanged</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 commit ebbb3e2 (snap pre-deploy-kkb-hi-out-...040146 / kkb-kn-out-...040147)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Flow VALIDATED live (7e5e1173/ab930586: get_profile always first, create before apply, no false success). Apply itself blocked by backend 404 (issue #42).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>kkb-kn-out endpoint PATCH (get_profile/apply_job)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>kkb-kn-out 87ab9108</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Briefly re-pointed to UP hosts on a wrong drift-hypothesis; REVERTED on owner correction ('Karnataka doesn't use those endpoints')</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 (snap raya/snapshots/kkb-kn-out.tools.pre-endpoint-fix.json)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>REVERTED - net change none; back on Karnataka endpoints, instructions intact (analyser C10 corrected)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Combined bot (file)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Lines out-&gt;combined</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Review verdict</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Gaps to close before deploy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>kkb-hi-combined.md</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1366-&gt;1615 (+249)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>PASS (additive, math-verified)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>v0 built, NOT deployed</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Shared No-Match/Hallucination-Guard/Pre-check assume ${recommendations} (unset on inbound); permission-to-fetch not gated (inbound fetches silently). Outbound branch is byte-identical to today's kkb-hi-out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>kkb-kn-combined.md</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1364-&gt;1690</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>FIX_NEEDED</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>v0 built, NOT deployed</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Same inbound gaps as kkb-hi PLUS inherited kkb-kn-in inventory-prose contradiction (Karnataka JSON vs UP/Burger-King descriptor prose) - open-items#11. Fix that first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>maya-hi-combined.md</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1140-&gt;1436</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>v0 built, NOT deployed</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Same inbound gaps; Maya additionally still carries the ${new_seeker} branch (unsubstituted on inbound). Preserve Maya divergences (campus identity, feminine voice, MPL, Experience Capture).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>dkb-hi-combined.md</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>911-&gt;964</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>v0 built, NOT deployed</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Folded inbound greeting references a non-existent 'Inbound Routing Rule' section (shared outbound Phase Entry Rule kept). Builder: degrades to Phase-3 new-job capture, but dangling refs should be resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>dkb-kn-combined.md</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>893-&gt;953</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>v0 built, NOT deployed</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Same dangling 'Inbound Routing Rule' refs as dkb-hi. Kannada twin.</t>
         </is>
       </c>
     </row>

--- a/reports/overnight-2026-07-30.xlsx
+++ b/reports/overnight-2026-07-30.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2088,9 +2088,44 @@
           <t>design</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>v0 built + reviewed; NOT deployed - needs a direction-aware v1 pass (REPORT G.5)</t>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>RESOLVED via v1 direction-aware pass; 5 experimental agents created (REPORT G.5/G.6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>combined bots (5)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKER</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>${call_direction} is NOT injected on POST /api/call (absent from agent_args, also on real standalone outbound) -&gt; combined branch ambiguous -&gt; bot defaults to INBOUND (used hardcoded inventory not ${recommendations}, welcome greeting) on an OUTBOUND trigger</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Flagged - open-items#12; needs LitWiz/Raya to confirm when/how call_direction is set; combined approach unvalidated until then - repro b2e9e1e9</t>
         </is>
       </c>
     </row>
@@ -2105,10 +2140,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
@@ -2409,6 +2444,33 @@
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Clean phone +917946350285 -&gt; get_profile empty -&gt; create_profile SUCCESS (profileId 5822b168) -&gt; apply_job 404 'Invalid or missing profile_id' on Karnataka BAP (issue #42, backend). new_seeker-removal VALIDATED; apply blocked by backend, not prompt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>kkb-hi-combined 3f521174</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>OUTBOUND smoke (call_direction check)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>b2e9e1e9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>BLOCKER FOUND</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Triggered OUTBOUND with real ${recommendations}, but the bot ran the INBOUND branch: welcome greeting + presented hardcoded-inventory jobs (CY Future/Weavings), NOT the passed recommendations. agent_args has NO call_direction (issue #46). Combined approach unvalidated until platform confirms call_direction injection.</t>
         </is>
       </c>
     </row>
@@ -2744,27 +2806,27 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Combined bot (file)</t>
+          <t>Combined bot</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Lines out-&gt;combined</t>
+          <t>v1 agent uuid (deploy=false)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Review verdict</t>
+          <t>v1 review</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -2774,73 +2836,73 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Gaps to close before deploy</t>
+          <t>BLOCKER + residual gaps</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>kkb-hi-combined.md</t>
+          <t>kkb-hi-combined</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1366-&gt;1615 (+249)</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>PASS (additive, math-verified)</t>
+          <t>3f521174</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>outbound OK / inbound FIX_NEEDED</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>v0 built, NOT deployed</t>
+          <t>v1 built + agent CREATED</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Shared No-Match/Hallucination-Guard/Pre-check assume ${recommendations} (unset on inbound); permission-to-fetch not gated (inbound fetches silently). Outbound branch is byte-identical to today's kkb-hi-out.</t>
+          <t>BLOCKER: call_direction NOT injected (open-items#12) - smoke test b2e9e1e9 ran INBOUND (inventory+welcome) on an outbound trigger. Residual: inbound No-Match wording, hr_contact share, sample convos are outbound examples.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>kkb-kn-combined.md</t>
+          <t>kkb-kn-combined</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1364-&gt;1690</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>FIX_NEEDED</t>
+          <t>f38da775</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>FIX_NEEDED -&gt; structural gaps fixed</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>v0 built, NOT deployed</t>
+          <t>v1 built + agent CREATED</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Same inbound gaps as kkb-hi PLUS inherited kkb-kn-in inventory-prose contradiction (Karnataka JSON vs UP/Burger-King descriptor prose) - open-items#11. Fix that first.</t>
+          <t>BLOCKER: call_direction (#12). Fixed: inbound fetch-gate annotations + Kannada inventory prose rewritten to Karnataka (0 UP leftovers). Residual: inbound spoken nuance.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>maya-hi-combined.md</t>
+          <t>maya-hi-combined</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1140-&gt;1436</t>
+          <t>904f333f</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2850,51 +2912,51 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>v0 built, NOT deployed</t>
+          <t>v1 built + agent CREATED</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Same inbound gaps; Maya additionally still carries the ${new_seeker} branch (unsubstituted on inbound). Preserve Maya divergences (campus identity, feminine voice, MPL, Experience Capture).</t>
+          <t>BLOCKER: call_direction (#12). ${new_seeker} gated for inbound; Maya divergences preserved. Residual: inbound sample convos + MPL cross-call policy nuance.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>dkb-hi-combined.md</t>
+          <t>dkb-hi-combined</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>911-&gt;964</t>
+          <t>fabda71d</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>outbound OK / inbound FIX_NEEDED</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>v0 built, NOT deployed</t>
+          <t>v1 built + agent CREATED</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Folded inbound greeting references a non-existent 'Inbound Routing Rule' section (shared outbound Phase Entry Rule kept). Builder: degrades to Phase-3 new-job capture, but dangling refs should be resolved.</t>
+          <t>BLOCKER: call_direction (#12). Residual: Phase-3 job-capture entry is outbound-flavored; create_job companyName + update_job phone are outbound variants.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>dkb-kn-combined.md</t>
+          <t>dkb-kn-combined</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>893-&gt;953</t>
+          <t>847a85e2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2904,12 +2966,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>v0 built, NOT deployed</t>
+          <t>v1 built + agent CREATED</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Same dangling 'Inbound Routing Rule' refs as dkb-hi. Kannada twin.</t>
+          <t>BLOCKER: call_direction (#12). Kannada twin; inbound routing folded. Residual: minor outbound-framed shared headers.</t>
         </is>
       </c>
     </row>
